--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
@@ -12,12 +12,18 @@
     <sheet name="IS" r:id="rId6" sheetId="4"/>
     <sheet name="Hypertension" r:id="rId7" sheetId="5"/>
     <sheet name="T2DM" r:id="rId8" sheetId="6"/>
+    <sheet name="Sheet6" r:id="rId9" sheetId="7"/>
+    <sheet name="Sheet7" r:id="rId10" sheetId="8"/>
+    <sheet name="Sheet8" r:id="rId11" sheetId="9"/>
+    <sheet name="Sheet9" r:id="rId12" sheetId="10"/>
+    <sheet name="Sheet10" r:id="rId13" sheetId="11"/>
+    <sheet name="Sheet11" r:id="rId14" sheetId="12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -78,6 +84,12 @@
   <si>
     <t>rs80107551</t>
   </si>
+  <si>
+    <t>CI_LOW</t>
+  </si>
+  <si>
+    <t>CI_HIGH</t>
+  </si>
 </sst>
 </file>
 
@@ -311,6 +323,582 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14963254700179737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.41797490772594814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11870981372235342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13690936771640347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2744239202684682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.15694180532598825</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4946739007594948</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.18079029010751826</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17231229358852374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3624014710389068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.13247889831789209</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5398065244600002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.274848727824216</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20782021741944293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.523819546186257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.13713453236173637</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.48198501803409766</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2077159533106249</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17594412534304146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.43573180339057077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.16293333255494152</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4327418526773308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.10687518756744774</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13765740822570882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2365656169325301</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.12663846668762802</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4299986582489812</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.17672172487372517</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1547756079394659</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4132390694450828</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.14170824330234622</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.41140145792647415</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12798497132178172</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13759857888986118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3030724175890595</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001256794488496452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06843409582139569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0709476847983886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03555657668872048</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9718035805028898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04688229928602027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03147062787208226</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1252352264441228</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03997598324392986</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.24089140889934385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03296004831275466</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07779612496989799</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1437162215954073</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05650825167482278</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5597058331090312</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03026391872846553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.11748378884629831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05695595138936726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04449993373358816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4964480621859819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0029714180325279803</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07017452255500528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06423168648994931</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03428729822575372</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.930939899650901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0031784175785706174</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09076925637809445</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08441242122095323</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04468920346914482</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9433000882701773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.2971520096230394E-4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07748570839242619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07814513879435081</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03970174673132067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9933738017601925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3886014068137135</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20365214618346125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5735506674439658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09436186766849605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.818368616903005E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48281768772319755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2719336310970878</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6937017443493073</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.10759390644189275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.2095144208032765E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3800634414797113</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06654160519881264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.69358527776061</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1599601205514789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01750199801816605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2382257280971429</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.027188700718636882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4492627554756489</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10767195274413573</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.026931153767517008</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3870995753642745</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1797021884114889</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5944969623170601</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.10581499334325795</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.539257189368221E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.34696220429828</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1300123057483675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5639121028481925</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11068872374995536</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0017210273361036622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3998744391804769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.22381089042685845</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5759379879340953</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08982834120082574</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.525671281459244E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -1269,4 +1857,580 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.3657941859084055</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.6404566650240828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.0911317067927282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.14013391791616192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.912204594734816E-22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.597594431739882</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.7609670638308441</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.43422179964892</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08335338371987858</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.046574888263033E-82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.4284435055405154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.8895995361272275</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9672874749538032</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.23528368907485314</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.269943459095527E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.136148241004573</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3025481974449946</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9697482845641513</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08489793695939879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.650989930822831E-41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.3703530783155036</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.675618511269891</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0650876453611162</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15574766987468738</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.3859986741418282E-18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.2835533136291235</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.5849840369632524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9821225902949947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1537911853745555</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.056688265761653E-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.3599940408060434</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.6632045693177842</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0567835122943026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.15469924924068407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4795384752497932E-18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5821448812046267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4456055952492079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7186841671600455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06966290099766266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.455263607305305E-17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6518724612238195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.47992924989450925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8238156725531297</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08772612822923992</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.079693599189901E-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6321389961444899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4251872512041577</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8390907410848221</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10558762496955723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.139224560490123E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5125458130906491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.33725328401706073</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6878383421642373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08943496381305527</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.987953378607802E-9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.582090657946413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.44480533329476313</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7193759825980629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07004353298553566</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.536989836238003E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.524419290739908</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3701397403817621</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6786988410980539</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07871405630517646</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.695136583557227E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5856887924749857</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.44843125961623764</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7229463253337338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07002935349936128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.08971027230661E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5440212847626991</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3621864547316229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7258561147937752</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09277287246483476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.518134154701415E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6079789868716109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.373809598175852</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8421483755673698</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11947417790599943</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.603556268905657E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44936350875535735</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.16680201440245596</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7319250031082587</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14416402773107215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001826833704690536</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.43950924266974745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21896638595471674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6600520993847782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11252186567093404</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.384052858241705E-5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5560058305377472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38355140054814485</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7284602605273496</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08798695407632773</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6294653289165546E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5050007369353019</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29021682216880595</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7197846517017978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1095836299829061</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.058589360003513E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5470518228277412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34474018439671567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7493634612587667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.10322022368929876</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1589711924689232E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
@@ -18,12 +18,24 @@
     <sheet name="Sheet9" r:id="rId12" sheetId="10"/>
     <sheet name="Sheet10" r:id="rId13" sheetId="11"/>
     <sheet name="Sheet11" r:id="rId14" sheetId="12"/>
+    <sheet name="Sheet12" r:id="rId15" sheetId="13"/>
+    <sheet name="Sheet13" r:id="rId16" sheetId="14"/>
+    <sheet name="Sheet14" r:id="rId17" sheetId="15"/>
+    <sheet name="Sheet15" r:id="rId18" sheetId="16"/>
+    <sheet name="Sheet16" r:id="rId19" sheetId="17"/>
+    <sheet name="Sheet17" r:id="rId20" sheetId="18"/>
+    <sheet name="Sheet18" r:id="rId21" sheetId="19"/>
+    <sheet name="Sheet19" r:id="rId22" sheetId="20"/>
+    <sheet name="Sheet20" r:id="rId23" sheetId="21"/>
+    <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
+    <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
+    <sheet name="Sheet23" r:id="rId26" sheetId="24"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -899,6 +911,1350 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.3657941859084055</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.6404566650240828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.0911317067927282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.14013391791616192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.912204594734816E-22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.597594431739882</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.7609670638308441</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.43422179964892</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08335338371987858</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.046574888263033E-82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.4284435055405154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.8895995361272275</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9672874749538032</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.23528368907485314</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.269943459095527E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.136148241004573</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3025481974449946</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9697482845641513</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08489793695939879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.650989930822831E-41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.3703530783155036</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.675618511269891</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0650876453611162</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15574766987468738</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.3859986741418282E-18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.2835533136291235</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.5849840369632524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9821225902949947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1537911853745555</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.056688265761653E-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.3599940408060434</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.6632045693177842</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0567835122943026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.15469924924068407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4795384752497932E-18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5821448812046267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4456055952492079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7186841671600455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06966290099766266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.455263607305305E-17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6518724612238195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.47992924989450925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8238156725531297</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08772612822923992</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.079693599189901E-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6321389961444899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4251872512041577</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8390907410848221</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10558762496955723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.139224560490123E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5125458130906491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.33725328401706073</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6878383421642373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08943496381305527</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.987953378607802E-9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.582090657946413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.44480533329476313</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7193759825980629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07004353298553566</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.536989836238003E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.524419290739908</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3701397403817621</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6786988410980539</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07871405630517646</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.695136583557227E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5856887924749857</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.44843125961623764</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7229463253337338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07002935349936128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.08971027230661E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5440212847626991</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3621864547316229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7258561147937752</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09277287246483476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.518134154701415E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6079789868716109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.373809598175852</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8421483755673698</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11947417790599943</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.603556268905657E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44936350875535735</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.16680201440245596</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7319250031082587</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14416402773107215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001826833704690536</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.43950924266974745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21896638595471674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6600520993847782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11252186567093404</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.384052858241705E-5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5560058305377472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38355140054814485</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7284602605273496</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08798695407632773</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6294653289165546E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5050007369353019</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29021682216880595</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7197846517017978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1095836299829061</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.058589360003513E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5470518228277412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34474018439671567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7493634612587667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.10322022368929876</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1589711924689232E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14963254700179737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.41797490772594814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11870981372235342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13690936771640347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2744239202684682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.15694180532598825</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4946739007594948</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.18079029010751826</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17231229358852374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3624014710389068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.13247889831789209</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5398065244600002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.274848727824216</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20782021741944293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.523819546186257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.13713453236173637</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.48198501803409766</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2077159533106249</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17594412534304146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.43573180339057077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.16293333255494152</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4327418526773308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.10687518756744774</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13765740822570882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2365656169325301</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.12663846668762802</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4299986582489812</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.17672172487372517</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1547756079394659</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4132390694450828</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.14170824330234622</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.41140145792647415</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12798497132178172</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13759857888986118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3030724175890595</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001256794488496452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06843409582139569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0709476847983886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03555657668872048</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9718035805028898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04688229928602027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03147062787208226</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1252352264441228</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03997598324392986</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.24089140889934385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03296004831275466</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07779612496989799</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1437162215954073</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05650825167482278</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5597058331090312</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03026391872846553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.11748378884629831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05695595138936726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04449993373358816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4964480621859819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0029714180325279803</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07017452255500528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06423168648994931</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03428729822575372</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.930939899650901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0031784175785706174</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09076925637809445</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08441242122095323</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04468920346914482</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9433000882701773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.2971520096230394E-4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07748570839242619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07814513879435081</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03970174673132067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9933738017601925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3886014068137135</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20365214618346125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5735506674439658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09436186766849605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.818368616903005E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48281768772319755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2719336310970878</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6937017443493073</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.10759390644189275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.2095144208032765E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3800634414797113</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06654160519881264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.69358527776061</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1599601205514789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01750199801816605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2382257280971429</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.027188700718636882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4492627554756489</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10767195274413573</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.026931153767517008</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3870995753642745</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1797021884114889</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5944969623170601</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.10581499334325795</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.539257189368221E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.34696220429828</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1300123057483675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5639121028481925</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11068872374995536</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0017210273361036622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3998744391804769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.22381089042685845</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5759379879340953</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08982834120082574</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.525671281459244E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.3657941859084055</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.6404566650240828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.0911317067927282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.14013391791616192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.912204594734816E-22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.597594431739882</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.7609670638308441</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.43422179964892</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08335338371987858</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.046574888263033E-82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.4284435055405154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.8895995361272275</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9672874749538032</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.23528368907485314</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.269943459095527E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.136148241004573</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3025481974449946</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9697482845641513</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08489793695939879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.650989930822831E-41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.3703530783155036</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.675618511269891</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0650876453611162</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15574766987468738</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.3859986741418282E-18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.2835533136291235</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.5849840369632524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9821225902949947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1537911853745555</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.056688265761653E-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.3599940408060434</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.6632045693177842</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0567835122943026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.15469924924068407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4795384752497932E-18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -1084,6 +2440,966 @@
       </c>
       <c r="G8" t="n">
         <v>6.08971027230661E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5821448812046267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4456055952492079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7186841671600455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06966290099766266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.455263607305305E-17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6518724612238195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.47992924989450925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8238156725531297</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08772612822923992</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.079693599189901E-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6321389961444899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4251872512041577</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8390907410848221</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10558762496955723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.139224560490123E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5125458130906491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.33725328401706073</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6878383421642373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08943496381305527</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.987953378607802E-9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.582090657946413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.44480533329476313</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7193759825980629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07004353298553566</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.536989836238003E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.524419290739908</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3701397403817621</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6786988410980539</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07871405630517646</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.695136583557227E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5856887924749857</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.44843125961623764</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7229463253337338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07002935349936128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.08971027230661E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5440212847626991</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3621864547316229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7258561147937752</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09277287246483476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.518134154701415E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6079789868716109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.373809598175852</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8421483755673698</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11947417790599943</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.603556268905657E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44936350875535735</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.16680201440245596</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7319250031082587</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14416402773107215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001826833704690536</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.43950924266974745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21896638595471674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6600520993847782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11252186567093404</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.384052858241705E-5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5560058305377472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38355140054814485</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7284602605273496</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08798695407632773</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6294653289165546E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5050007369353019</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29021682216880595</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7197846517017978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1095836299829061</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.058589360003513E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5470518228277412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34474018439671567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7493634612587667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.10322022368929876</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1589711924689232E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14963254700179737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.41797490772594814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11870981372235342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13690936771640347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2744239202684682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.15694180532598825</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4946739007594948</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.18079029010751826</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17231229358852374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3624014710389068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.13247889831789209</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5398065244600002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.274848727824216</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20782021741944293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.523819546186257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.13713453236173637</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.48198501803409766</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2077159533106249</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17594412534304146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.43573180339057077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.16293333255494152</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4327418526773308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.10687518756744774</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13765740822570882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2365656169325301</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.12663846668762802</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4299986582489812</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.17672172487372517</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1547756079394659</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4132390694450828</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.14170824330234622</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.41140145792647415</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12798497132178172</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13759857888986118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3030724175890595</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001256794488496452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06843409582139569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0709476847983886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03555657668872048</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9718035805028898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04688229928602027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03147062787208226</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1252352264441228</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03997598324392986</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.24089140889934385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03296004831275466</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07779612496989799</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1437162215954073</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05650825167482278</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5597058331090312</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03026391872846553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.11748378884629831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05695595138936726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04449993373358816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4964480621859819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0029714180325279803</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07017452255500528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06423168648994931</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03428729822575372</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.930939899650901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0031784175785706174</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09076925637809445</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08441242122095323</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04468920346914482</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9433000882701773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.2971520096230394E-4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07748570839242619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07814513879435081</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03970174673132067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9933738017601925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3886014068137135</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20365214618346125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5735506674439658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09436186766849605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.818368616903005E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48281768772319755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2719336310970878</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6937017443493073</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.10759390644189275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.2095144208032765E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3800634414797113</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06654160519881264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.69358527776061</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1599601205514789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01750199801816605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2382257280971429</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.027188700718636882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4492627554756489</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10767195274413573</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.026931153767517008</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3870995753642745</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1797021884114889</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5944969623170601</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.10581499334325795</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.539257189368221E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.34696220429828</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1300123057483675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5639121028481925</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11068872374995536</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0017210273361036622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3998744391804769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.22381089042685845</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5759379879340953</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08982834120082574</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.525671281459244E-6</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
@@ -30,12 +30,18 @@
     <sheet name="Sheet21" r:id="rId24" sheetId="22"/>
     <sheet name="Sheet22" r:id="rId25" sheetId="23"/>
     <sheet name="Sheet23" r:id="rId26" sheetId="24"/>
+    <sheet name="Sheet24" r:id="rId27" sheetId="25"/>
+    <sheet name="Sheet25" r:id="rId28" sheetId="26"/>
+    <sheet name="Sheet26" r:id="rId29" sheetId="27"/>
+    <sheet name="Sheet27" r:id="rId30" sheetId="28"/>
+    <sheet name="Sheet28" r:id="rId31" sheetId="29"/>
+    <sheet name="Sheet29" r:id="rId32" sheetId="30"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -3407,6 +3413,966 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.3198261799425832</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.5960433648474326</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.0436089950377339</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.14092713515553543</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7.582802042001386E-21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.532972244118638</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.708579298157406</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.35736519007987</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08959543573406532</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.251351585378545E-65</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.3712995192709168</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.8356315934689993</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9069674450728342</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.23690411948881762</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.1053401770449115E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.0891850758913781</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.2482527215025185</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9301174302802377</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0811569620465002</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.5723293415507687E-41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.331754598839098</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.6305789094986352</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0329302881795608</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15246138298955977</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.4359366969551824E-18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.2289730134305326</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.5098846717395815</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9480613551214836</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.14332227464747394</v>
+      </c>
+      <c r="G7" t="n">
+        <v>9.917989715665893E-18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.3149090038197864</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.6222799056053732</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0075381020341996</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.15682188866611568</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.0842844282414456E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5603103738924813</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4281584206234528</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6924623271615098</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06742446595358598</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.554596145322953E-17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6219722968062266</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4563847643071988</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.7875598293052544</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08448343494848355</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.8109064840624832E-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6011712149437</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.40189026184648147</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8004521680409185</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10167395566184617</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.3647210663825447E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.48685044473137296</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.3194519268255359</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.65424896263721</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0854074070948148</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.195753977056901E-8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5629418347958358</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.42949872721520677</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.6963849423764649</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.06808321815338217</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.357260135925061E-16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5007462217040558</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3533302257866141</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6481622176214975</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07521224281502126</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.7800312058806596E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5645453462927961</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.43157443394037087</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6975162586452213</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0678423022206251</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.690425967082543E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5182257460000596</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.32384806026798046</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7126034317321386</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09917228863881586</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.7367611223103537E-7</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.5717022530055085</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.3137471140877275</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8296573919232895</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1316097647539699</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.3996267796228138E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.4144885981540191</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.11583966262128037</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7131375336867578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1523719058840504</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.006523397418915035</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.40976071642805206</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.19496204724372918</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.624559385612375</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10959115774710351</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.847579004538423E-4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5361996313690603</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.35941443829989667</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.712984824438224</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.09019652707610393</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.7680739163519404E-9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.47457788738045775</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2518753432678898</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6972804314930257</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11362374699620814</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.957048339590861E-5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5218351872257071</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.30547423583299793</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7381961386184163</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.11038824050648427</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.2755687156183146E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14043945990236797</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.40018083022286965</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11930191041813368</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1325211073063784</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2892576060076933</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.14418966359284668</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.46951322873587925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.18113390155018588</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.16598141078726153</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.38500592785057175</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.11772739016904024</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.510113013424699</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.2746582330866184</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20019674655900954</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5564930552125543</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.12434466634771549</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.45370672895910924</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2050173962636783</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.16804186867928256</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.45932280266275627</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.15836703031163035</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.42064495142911357</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.10391089080585286</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13381526587626694</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2366209235371974</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.1169155146943046</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4068002094274701</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.17296918003886086</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.14790035445569666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4292346992867377</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.132190816708004</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.3934708665571349</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12908923314112694</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13330614788220968</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.32137643391404164</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.003878480276442189</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06349978240120158</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.07125674295408596</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0343766646314509</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9101708409034004</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04874971361482058</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.02672133553614857</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.12422076276578974</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03850563732192304</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.20549842213547728</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03755435109862686</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.06730337695034971</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.14241207914760343</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05349884084131458</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4827005561996967</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.023596159344900326</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.10848538247463713</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.06129306378483648</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04331082812741674</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5858844055805644</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0015732487817076135</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0669379985032733</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06379150093985807</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03334936210283963</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9623739287049794</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.342102091179028E-4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.08321437763263886</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08428279805087466</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04272887134783508</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9900248482860522</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.002937170248417374</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07239813006247947</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07827247055931422</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03843637770964125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9390878093029699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -3592,6 +4558,198 @@
       </c>
       <c r="G8" t="n">
         <v>1.1589711924689232E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3713318452006961</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.18458369700340496</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5580799933979873</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09527966744759753</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9.72778484106058E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.4563813052196278</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.23476571902341298</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6779968914158425</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11306917663072184</v>
+      </c>
+      <c r="G3" t="n">
+        <v>5.430038995001046E-5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3551539542837967</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.0405732775521665</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.6697346310154269</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1605003452712399</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.026911957166705705</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.22463694196069872</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.023036347902695598</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.42623753601870185</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10285744594796078</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.02896490573703312</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3710988455134618</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.16031022365970912</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5818874673672144</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.10754521523150647</v>
+      </c>
+      <c r="G6" t="n">
+        <v>5.592778233369169E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.3280550709146371</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1152993933973745</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5408107484318997</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.10854881505982786</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.002509535310967206</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3834836651575658</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.20439417617789393</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5625731541372377</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.09137218825493464</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2.7054461160903165E-5</v>
       </c>
     </row>
   </sheetData>

--- a/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
+++ b/SensitivityAnalysis/LeaveOneOut/BinaryData_SA/loo.xlsx
@@ -36,12 +36,18 @@
     <sheet name="Sheet27" r:id="rId30" sheetId="28"/>
     <sheet name="Sheet28" r:id="rId31" sheetId="29"/>
     <sheet name="Sheet29" r:id="rId32" sheetId="30"/>
+    <sheet name="Sheet30" r:id="rId33" sheetId="31"/>
+    <sheet name="Sheet31" r:id="rId34" sheetId="32"/>
+    <sheet name="Sheet32" r:id="rId35" sheetId="33"/>
+    <sheet name="Sheet33" r:id="rId36" sheetId="34"/>
+    <sheet name="Sheet34" r:id="rId37" sheetId="35"/>
+    <sheet name="Sheet35" r:id="rId38" sheetId="36"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="22">
   <si>
     <t>SNPS</t>
   </si>
@@ -4757,6 +4763,1158 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.3657941859084055</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.6404566650240828</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.0911317067927282</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.14013391791616192</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.912204594734816E-22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.597594431739882</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.7609670638308441</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.43422179964892</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08335338371987858</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.046574888263033E-82</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.4284435055405154</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.8895995361272275</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.9672874749538032</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.23528368907485314</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.269943459095527E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.136148241004573</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.3025481974449946</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.9697482845641513</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08489793695939879</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.650989930822831E-41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-1.3703530783155036</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.675618511269891</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.0650876453611162</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.15574766987468738</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.3859986741418282E-18</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-1.2835533136291235</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.5849840369632524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.9821225902949947</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1537911853745555</v>
+      </c>
+      <c r="G7" t="n">
+        <v>7.056688265761653E-17</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-1.3599940408060434</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-1.6632045693177842</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-1.0567835122943026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.15469924924068407</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.4795384752497932E-18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5821448812046267</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4456055952492079</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7186841671600455</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06966290099766266</v>
+      </c>
+      <c r="G2" t="n">
+        <v>6.455263607305305E-17</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6518724612238195</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.47992924989450925</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8238156725531297</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.08772612822923992</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.079693599189901E-13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.6321389961444899</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.4251872512041577</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8390907410848221</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.10558762496955723</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2.139224560490123E-9</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.5125458130906491</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.33725328401706073</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6878383421642373</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.08943496381305527</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.987953378607802E-9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.582090657946413</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.44480533329476313</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7193759825980629</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.07004353298553566</v>
+      </c>
+      <c r="G6" t="n">
+        <v>9.536989836238003E-17</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.524419290739908</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3701397403817621</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6786988410980539</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.07871405630517646</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.695136583557227E-11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5856887924749857</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.44843125961623764</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7229463253337338</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07002935349936128</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.08971027230661E-17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.5440212847626991</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.3621864547316229</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.7258561147937752</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09277287246483476</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4.518134154701415E-9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.6079789868716109</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.373809598175852</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8421483755673698</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.11947417790599943</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3.603556268905657E-7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.44936350875535735</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.16680201440245596</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7319250031082587</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.14416402773107215</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.001826833704690536</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.43950924266974745</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.21896638595471674</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.6600520993847782</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.11252186567093404</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.384052858241705E-5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.5560058305377472</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.38355140054814485</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.7284602605273496</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08798695407632773</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.6294653289165546E-10</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.5050007369353019</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.29021682216880595</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7197846517017978</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1095836299829061</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.058589360003513E-6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5470518228277412</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.34474018439671567</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.7493634612587667</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.10322022368929876</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.1589711924689232E-7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.14963254700179737</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.41797490772594814</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.11870981372235342</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.13690936771640347</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2744239202684682</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.15694180532598825</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.4946739007594948</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.18079029010751826</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.17231229358852374</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.3624014710389068</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.13247889831789209</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.5398065244600002</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.274848727824216</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20782021741944293</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.523819546186257</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.13713453236173637</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.48198501803409766</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.2077159533106249</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.17594412534304146</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.43573180339057077</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.16293333255494152</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.4327418526773308</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.10687518756744774</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.13765740822570882</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2365656169325301</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.12663846668762802</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.4299986582489812</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.17672172487372517</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1547756079394659</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.4132390694450828</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.14170824330234622</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.41140145792647415</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.12798497132178172</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.13759857888986118</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3030724175890595</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.001256794488496452</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.06843409582139569</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.0709476847983886</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.03555657668872048</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9718035805028898</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.04688229928602027</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.03147062787208226</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.1252352264441228</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.03997598324392986</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.24089140889934385</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.03296004831275466</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.07779612496989799</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1437162215954073</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.05650825167482278</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.5597058331090312</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.03026391872846553</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.11748378884629831</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05695595138936726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.04449993373358816</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4964480621859819</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0029714180325279803</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.07017452255500528</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.06423168648994931</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03428729822575372</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.930939899650901</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.0031784175785706174</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.09076925637809445</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.08441242122095323</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.04468920346914482</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9433000882701773</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3.2971520096230394E-4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.07748570839242619</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.07814513879435081</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.03970174673132067</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9933738017601925</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1"/>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3886014068137135</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.20365214618346125</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.5735506674439658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.09436186766849605</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3.818368616903005E-5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.48281768772319755</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2719336310970878</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6937017443493073</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.10759390644189275</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.2095144208032765E-6</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.3800634414797113</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.06654160519881264</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.69358527776061</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1599601205514789</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.01750199801816605</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.2382257280971429</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.027188700718636882</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.4492627554756489</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.10767195274413573</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.026931153767517008</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.3870995753642745</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1797021884114889</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.5944969623170601</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.10581499334325795</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2.539257189368221E-4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.34696220429828</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.1300123057483675</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.5639121028481925</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.11068872374995536</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0017210273361036622</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.3998744391804769</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.22381089042685845</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.5759379879340953</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.08982834120082574</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8.525671281459244E-6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
